--- a/demo_data/sample_ap_aging.xlsx
+++ b/demo_data/sample_ap_aging.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Tedarikçi</t>
   </si>
@@ -31,28 +31,28 @@
     <t>Para Birimi</t>
   </si>
   <si>
+    <t>Akıllı Yazılım Hizmetleri</t>
+  </si>
+  <si>
+    <t>Global Ambalaj San.</t>
+  </si>
+  <si>
+    <t>Anadolu Hammadde Ltd.</t>
+  </si>
+  <si>
     <t>Toptan Kağıt Tic.</t>
   </si>
   <si>
-    <t>Global Ambalaj San.</t>
-  </si>
-  <si>
-    <t>Yıldız Nakliyat</t>
-  </si>
-  <si>
-    <t>Pak Kimyasal Ürünler</t>
-  </si>
-  <si>
-    <t>Demir Metal İşleme</t>
-  </si>
-  <si>
-    <t>Bora Elektrik Malz.</t>
-  </si>
-  <si>
-    <t>Kuzey Plastik</t>
-  </si>
-  <si>
-    <t>Efe Gıda Toptan</t>
+    <t>Merkez Enerji AŞ</t>
+  </si>
+  <si>
+    <t>Standart Kimyasallar AŞ</t>
+  </si>
+  <si>
+    <t>Pro Lojistik Hizmetleri</t>
+  </si>
+  <si>
+    <t>Bölge Bakım Onarım</t>
   </si>
   <si>
     <t>BL2000</t>
@@ -64,9 +64,15 @@
     <t>BL2002</t>
   </si>
   <si>
+    <t>BL2003</t>
+  </si>
+  <si>
     <t>BL2004</t>
   </si>
   <si>
+    <t>BL2005</t>
+  </si>
+  <si>
     <t>BL2006</t>
   </si>
   <si>
@@ -92,6 +98,33 @@
   </si>
   <si>
     <t>BL2014</t>
+  </si>
+  <si>
+    <t>BL2015</t>
+  </si>
+  <si>
+    <t>BL2016</t>
+  </si>
+  <si>
+    <t>BL2017</t>
+  </si>
+  <si>
+    <t>BL2018</t>
+  </si>
+  <si>
+    <t>BL2019</t>
+  </si>
+  <si>
+    <t>BL2020</t>
+  </si>
+  <si>
+    <t>BL2021</t>
+  </si>
+  <si>
+    <t>BL2022</t>
+  </si>
+  <si>
+    <t>BL2023</t>
   </si>
   <si>
     <t>TL</t>
@@ -102,10 +135,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -121,7 +162,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -129,12 +170,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -430,23 +489,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -457,65 +516,65 @@
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1">
-        <v>46022</v>
+      <c r="C2" s="2">
+        <v>46037</v>
       </c>
       <c r="D2">
-        <v>144784</v>
+        <v>64592</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1">
-        <v>45982</v>
+      <c r="C3" s="2">
+        <v>46002</v>
       </c>
       <c r="D3">
-        <v>105375</v>
+        <v>72196</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1">
-        <v>45982</v>
+      <c r="C4" s="2">
+        <v>45948</v>
       </c>
       <c r="D4">
-        <v>57791</v>
+        <v>67514</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1">
-        <v>46032</v>
+      <c r="C5" s="2">
+        <v>45936</v>
       </c>
       <c r="D5">
-        <v>122851</v>
+        <v>16236</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -525,150 +584,337 @@
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1">
-        <v>46012</v>
+      <c r="C6" s="2">
+        <v>45947</v>
       </c>
       <c r="D6">
-        <v>50397</v>
+        <v>9734</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1">
-        <v>46032</v>
+      <c r="C7" s="2">
+        <v>46030</v>
       </c>
       <c r="D7">
-        <v>134795</v>
+        <v>16108</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1">
-        <v>46032</v>
+      <c r="C8" s="2">
+        <v>46030</v>
       </c>
       <c r="D8">
-        <v>101096</v>
+        <v>42462</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1">
-        <v>46012</v>
+      <c r="C9" s="2">
+        <v>45985</v>
       </c>
       <c r="D9">
-        <v>131074</v>
+        <v>8676</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="1">
-        <v>46032</v>
+      <c r="C10" s="2">
+        <v>45967</v>
       </c>
       <c r="D10">
-        <v>50023</v>
+        <v>51391</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1">
-        <v>46032</v>
+      <c r="C11" s="2">
+        <v>45978</v>
       </c>
       <c r="D11">
-        <v>112806</v>
+        <v>7417</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1">
-        <v>45982</v>
+      <c r="C12" s="2">
+        <v>45972</v>
       </c>
       <c r="D12">
-        <v>91830</v>
+        <v>33647</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1">
-        <v>45997</v>
+      <c r="C13" s="2">
+        <v>45992</v>
       </c>
       <c r="D13">
-        <v>67614</v>
+        <v>32527</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1">
-        <v>46032</v>
+      <c r="C14" s="2">
+        <v>45950</v>
       </c>
       <c r="D14">
-        <v>82015</v>
+        <v>7972</v>
       </c>
       <c r="E14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46014</v>
+      </c>
+      <c r="D15">
+        <v>30250</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46038</v>
+      </c>
+      <c r="D16">
+        <v>60460</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2">
+        <v>45933</v>
+      </c>
+      <c r="D17">
+        <v>8002</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2">
+        <v>45957</v>
+      </c>
+      <c r="D18">
+        <v>26110</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46043</v>
+      </c>
+      <c r="D19">
+        <v>50082</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46079</v>
+      </c>
+      <c r="D20">
+        <v>9387</v>
+      </c>
+      <c r="E20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46078</v>
+      </c>
+      <c r="D21">
+        <v>44194</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46047</v>
+      </c>
+      <c r="D22">
+        <v>74587</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45972</v>
+      </c>
+      <c r="D23">
+        <v>37677</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46001</v>
+      </c>
+      <c r="D24">
+        <v>39559</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45970</v>
+      </c>
+      <c r="D25">
+        <v>39220</v>
+      </c>
+      <c r="E25" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
